--- a/data/trans_orig/P39B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023</t>
+          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7199</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1293</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7261</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6695</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6093</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>353825</t>
+          <t>350879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378542</t>
+          <t>378223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>278428</t>
+          <t>280903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300239</t>
+          <t>300271</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>641860</t>
+          <t>642491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>673986</t>
+          <t>673967</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>28681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19886</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24985</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>384103</t>
+          <t>384130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>409345</t>
+          <t>408616</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>471570</t>
+          <t>473260</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>496224</t>
+          <t>495635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>864270</t>
+          <t>864882</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>898718</t>
+          <t>899266</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27469</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41166</t>
+          <t>41536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17847</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>495351</t>
+          <t>493895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>514637</t>
+          <t>514772</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>504007</t>
+          <t>504609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>519480</t>
+          <t>519980</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1005982</t>
+          <t>1004870</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1031139</t>
+          <t>1029474</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18067</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,47 +2483,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>19578</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>13441</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>29438</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>19578</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>13228</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>28974</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>829575</t>
+          <t>830273</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>868283</t>
+          <t>868177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>668904</t>
+          <t>669884</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>685871</t>
+          <t>685925</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1509455</t>
+          <t>1507739</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1552061</t>
+          <t>1550659</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23064</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32788</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>490845</t>
+          <t>490065</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514014</t>
+          <t>514136</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>500461</t>
+          <t>500280</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>516058</t>
+          <t>515661</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>997562</t>
+          <t>996003</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1026139</t>
+          <t>1024613</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>29654</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>53550</t>
+          <t>51681</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>332</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>321265</t>
+          <t>321373</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>337402</t>
+          <t>336839</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>558523</t>
+          <t>558300</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>587791</t>
+          <t>587690</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>885109</t>
+          <t>885193</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>928257</t>
+          <t>927258</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18484</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>30774</t>
+          <t>30316</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,74 +4607,74 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>3431</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>7597</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10569</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>16730</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>3431</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>7991</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>10569</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>4811</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>17138</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>219156</t>
+          <t>219097</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>236498</t>
+          <t>236797</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>321580</t>
+          <t>321284</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>339711</t>
+          <t>339954</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>547495</t>
+          <t>547173</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>573049</t>
+          <t>572048</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>28278</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>41722</t>
+          <t>41288</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>59980</t>
+          <t>59668</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18573</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>41030</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>74841</t>
+          <t>76102</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44956</t>
+          <t>43238</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>83598</t>
+          <t>83456</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3148228</t>
+          <t>3149617</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3230814</t>
+          <t>3231408</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3352878</t>
+          <t>3355173</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3420231</t>
+          <t>3420313</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6522834</t>
+          <t>6518804</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6623232</t>
+          <t>6621175</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>120525</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>69773</t>
+          <t>71929</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>110088</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>159994</t>
+          <t>160287</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>216101</t>
+          <t>218099</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>32094</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>63600</t>
+          <t>63588</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>61243</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>99425</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Edad-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>367494</t>
+          <t>362615</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>350879</t>
+          <t>345697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378223</t>
+          <t>374989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>293387</t>
+          <t>340363</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>280903</t>
+          <t>324480</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300271</t>
+          <t>348406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>660880</t>
+          <t>702978</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>642491</t>
+          <t>679471</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>673967</t>
+          <t>719790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>37591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>387634</t>
+          <t>392981</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>387634</t>
+          <t>392981</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>387634</t>
+          <t>392981</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>304504</t>
+          <t>353853</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>304504</t>
+          <t>353853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>304504</t>
+          <t>353853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>692137</t>
+          <t>746834</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>692137</t>
+          <t>746834</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>692137</t>
+          <t>746834</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>399085</t>
+          <t>448867</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>384130</t>
+          <t>434667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>408616</t>
+          <t>459505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>485137</t>
+          <t>460606</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>473260</t>
+          <t>447956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>495635</t>
+          <t>471736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>884222</t>
+          <t>909473</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>864882</t>
+          <t>888171</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>899266</t>
+          <t>925434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,67 +1781,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>32335</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>20886</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>47460</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>26733</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>16759</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>41536</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>422091</t>
+          <t>474498</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>422091</t>
+          <t>474498</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>422091</t>
+          <t>474498</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>508636</t>
+          <t>492550</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>508636</t>
+          <t>492550</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>508636</t>
+          <t>492550</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>930727</t>
+          <t>967048</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>930727</t>
+          <t>967048</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>930727</t>
+          <t>967048</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>19667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>506424</t>
+          <t>579416</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>493895</t>
+          <t>566004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>514772</t>
+          <t>589441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>512867</t>
+          <t>582831</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>504609</t>
+          <t>573267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>519980</t>
+          <t>590441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1019292</t>
+          <t>1162247</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1004870</t>
+          <t>1145642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1029474</t>
+          <t>1175832</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,67 +2463,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>29057</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>19591</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>39945</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>3,26%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>19578</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>13441</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>29438</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>12482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>529523</t>
+          <t>611891</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>529523</t>
+          <t>611891</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>529523</t>
+          <t>611891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>534899</t>
+          <t>611829</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>534899</t>
+          <t>611829</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>534899</t>
+          <t>611829</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1064422</t>
+          <t>1223720</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1064422</t>
+          <t>1223720</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1064422</t>
+          <t>1223720</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18478</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,67 +2919,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>11693</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6887</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>19182</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>10183</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>4809</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>17618</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>848390</t>
+          <t>655855</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>830273</t>
+          <t>641936</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>868177</t>
+          <t>666378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>678689</t>
+          <t>698410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>669884</t>
+          <t>688417</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>685925</t>
+          <t>705240</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1527079</t>
+          <t>1354265</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1507739</t>
+          <t>1338200</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1550659</t>
+          <t>1368047</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>25857</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20179</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15482</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24925</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>880790</t>
+          <t>691719</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>880790</t>
+          <t>691719</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>880790</t>
+          <t>691719</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>704504</t>
+          <t>727823</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>704504</t>
+          <t>727823</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>704504</t>
+          <t>727823</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1585294</t>
+          <t>1419542</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1585294</t>
+          <t>1419542</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1585294</t>
+          <t>1419542</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,27 +3488,27 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>12673</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>503571</t>
+          <t>543558</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>490065</t>
+          <t>530248</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514136</t>
+          <t>554854</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>508512</t>
+          <t>564708</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>500280</t>
+          <t>554895</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>515661</t>
+          <t>571956</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1012082</t>
+          <t>1108265</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>996003</t>
+          <t>1090054</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1024613</t>
+          <t>1122489</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>27965</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>38163</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>39311</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>29654</t>
+          <t>34929</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>58822</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11010</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>547189</t>
+          <t>592199</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>547189</t>
+          <t>592199</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>547189</t>
+          <t>592199</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>538968</t>
+          <t>598688</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>538968</t>
+          <t>598688</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>538968</t>
+          <t>598688</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1086156</t>
+          <t>1190886</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1086156</t>
+          <t>1190886</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1086156</t>
+          <t>1190886</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>14756</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>329828</t>
+          <t>363678</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>321373</t>
+          <t>353109</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>336839</t>
+          <t>371908</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>573502</t>
+          <t>401832</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>558300</t>
+          <t>394099</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>587690</t>
+          <t>408443</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>903331</t>
+          <t>765510</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>885193</t>
+          <t>753110</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>927258</t>
+          <t>775506</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -4474,102 +4474,102 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>14941</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>22543</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>30501</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>8873</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>2332</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>16057</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>20640</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>10238</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>30316</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>18004</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>356025</t>
+          <t>394208</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>356025</t>
+          <t>394208</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>356025</t>
+          <t>394208</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>595623</t>
+          <t>425959</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>595623</t>
+          <t>425959</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>595623</t>
+          <t>425959</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>951649</t>
+          <t>820167</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>951649</t>
+          <t>820167</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>951649</t>
+          <t>820167</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>11050</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>24364</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>228822</t>
+          <t>253758</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>219097</t>
+          <t>244294</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>236797</t>
+          <t>262338</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>331148</t>
+          <t>363733</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>321284</t>
+          <t>353132</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>339954</t>
+          <t>373403</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>559970</t>
+          <t>617491</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>547173</t>
+          <t>601702</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>572048</t>
+          <t>629951</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>15336</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>29376</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>38824</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>52767</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>41288</t>
+          <t>43692</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>59668</t>
+          <t>63848</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>265866</t>
+          <t>292410</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>265866</t>
+          <t>292410</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>265866</t>
+          <t>292410</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>383039</t>
+          <t>420281</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>383039</t>
+          <t>420281</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>383039</t>
+          <t>420281</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>648905</t>
+          <t>712691</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>648905</t>
+          <t>712691</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>648905</t>
+          <t>712691</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,27 +5499,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>37105</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>60049</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>53884</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>82903</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5612,67 +5612,67 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>52203</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>41482</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>32187</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>56904</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>33177</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>23582</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>43238</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>48644</t>
+          <t>58901</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>83456</t>
+          <t>94922</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3183614</t>
+          <t>3207747</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3149617</t>
+          <t>3174851</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3231408</t>
+          <t>3237412</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3383242</t>
+          <t>3412483</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3355173</t>
+          <t>3385023</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3420313</t>
+          <t>3436917</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>6566857</t>
+          <t>6620229</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6518804</t>
+          <t>6571021</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6621175</t>
+          <t>6656425</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>121619</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>100214</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>120525</t>
+          <t>144890</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>90573</t>
+          <t>103357</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>71929</t>
+          <t>86826</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>122365</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>224976</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>160287</t>
+          <t>199243</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>218099</t>
+          <t>256491</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>44012</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>63588</t>
+          <t>75820</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>78463</t>
+          <t>93588</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>61701</t>
+          <t>76322</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>99425</t>
+          <t>116593</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
